--- a/AAII_Financials/Quarterly/LEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>LEN</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
         <v>46081</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45991</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45900</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45808</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45716</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45626</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45535</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45443</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45351</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45260</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45169</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45077</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44985</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44895</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44804</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44712</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44620</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44530</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44439</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44347</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44255</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44165</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44074</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43982</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43890</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43799</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43708</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43616</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43524</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43434</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43343</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43159</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43069</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42978</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42886</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42794</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42704</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7939900</v>
+      </c>
+      <c r="E8" s="3">
         <v>6619500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9367600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8810300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8377500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7631500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9946900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9416000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8765600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7312900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10968200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8729600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8045200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6490400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10174400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8934400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14562200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6203500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8433600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6941400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11755700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5325500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6825900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5870300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5287400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4505300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6971500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5857100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>9431000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3868100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6459200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5672600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8439900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2980800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3785600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3261500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5599300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2337400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3376600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2833900</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6550700</v>
+      </c>
+      <c r="E9" s="3">
         <v>5487000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7666300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7104900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6743400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6021200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7558700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7214200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6605900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5551300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8098000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6426200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6089400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4980400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8116000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6799800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11260000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4937000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6425000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5435700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9390500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4280400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5506800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4807800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4455200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3895800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5870600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5014500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8194800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3404400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5477400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4909700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7545400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2649300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3178200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2744000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4828600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2037400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2871800</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2448500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1253400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1008200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1526300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1569100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1493300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1476800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2238100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2073000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2025000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1643200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2734600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2186200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1845400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1405800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2058400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2134600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3302200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1266500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2008600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1505700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2365200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1045100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1319100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1062500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>832200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>609500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1100900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>842600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1236200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>463700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>981800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>762900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>894500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>331500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>607400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>517500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>770700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>300000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>504800</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>385400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,55 +1496,58 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-14800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>22500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-99200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>32600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>70100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-102700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>50900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>21500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>36000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>15700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-25500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>24000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1535,18 +1555,18 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>-5100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-1500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-151500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
@@ -1554,100 +1574,103 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-61400</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>48900</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>12900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>12000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>128100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>104200</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
       <c r="AM14" s="3">
-        <v>140000</v>
+        <v>0</v>
       </c>
       <c r="AN14" s="3">
         <v>140000</v>
       </c>
-      <c r="AO14" s="3" t="s">
-        <v>8</v>
+      <c r="AO14" s="3">
+        <v>140000</v>
       </c>
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E15" s="3">
         <v>33400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>35000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>34200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>33800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>31300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>30400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>29400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>28600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>27100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>29000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>37100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>20300</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7521100</v>
+      </c>
+      <c r="E17" s="3">
         <v>6378300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8647200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8108000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7728900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6878600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8563000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7995100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7527200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6329700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9011700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7240300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6835200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5637200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8415600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7110200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12130600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5526800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6852800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5127000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9331800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3998500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5661200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5011200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4610800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4081800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6082800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5190000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8552400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3549000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5422700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5106700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7779600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2711400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3323600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2893100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>5240100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2287800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2915200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2494300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>418800</v>
+      </c>
+      <c r="E18" s="3">
         <v>241200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>720400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>702200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>648600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>752900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1383900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1420900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1238400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>983300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1956500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1489300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1209900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>853300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1758800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1824200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2431600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>676700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1580800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1814400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2423900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1327000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1164700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>859100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>676600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>423500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>888700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>667100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>878600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>319100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1036500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>565900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>660300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>269400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>462000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>368400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>359200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>49600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>461400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>339600</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,53 +2085,54 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-46400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-25900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-15400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-165100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-44200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>47300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>121000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>76800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>44800</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2174,141 +2208,147 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>471800</v>
+      </c>
+      <c r="E21" s="3">
         <v>321000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>754400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>725600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>708300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>799700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1404400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1615400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1311200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>963100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1864500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1528000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1156900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>828700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1787900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1842700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2471100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>696800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1600900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1835500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2468600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1349300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1190400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>883300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>700600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>444000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>917100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>689900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>919500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>337500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1061000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>591200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>701700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>289000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>481400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>385900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>388700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>61400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>475800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>352600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
         <v>13900</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>8</v>
@@ -2316,11 +2356,11 @@
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3">
         <v>18800</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
@@ -2328,11 +2368,11 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>15400</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>8</v>
@@ -2340,8 +2380,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>413200</v>
+      </c>
+      <c r="E23" s="3">
         <v>302500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>683000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>790700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>641900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>698200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1457900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1535100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1261100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>930800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1784100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1475200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1158600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>784500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1758700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1824300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2431600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>676700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1580800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1814400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2423900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1327000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1164600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>859000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>676600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>423600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>888700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>667100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>878500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>319100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1036500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>565900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>660200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>269400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>462000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>368400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>359200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>49600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>461400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>339600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E24" s="3">
         <v>69100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>185100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>190900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>160100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>169500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>358100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>347900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>210900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>416800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>358200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>280900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>185100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>414800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>351600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>599700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>167400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>387200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>405100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>570200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>310100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>273700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>189700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>160500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>32300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>217500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>154400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>220200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>79700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>238300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>98300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>140000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>64000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>164200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>124800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>128900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>20000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>150900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>106400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>308100</v>
+      </c>
+      <c r="E26" s="3">
         <v>233400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>498000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>599800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>481800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>528700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1099900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1187300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>960600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>719900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1367300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1117000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>877700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>599300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1343900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1472700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1831900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>509300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1193700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1409200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1853700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1016900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>890900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>669300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>516100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>391200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>671200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>512600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>658300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>239400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>798200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>467600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>520300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>205400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>297800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>243600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>230400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>29700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>310500</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>233100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>299700</v>
+      </c>
+      <c r="E27" s="3">
         <v>227000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>486500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>585700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>471200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>514700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1085900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1151800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>943600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>712400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1346000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1095800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>858200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>589900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1308900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1451600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1801600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>498600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1178100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1390200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1808900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>989000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>872800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>658600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>511100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>394100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>667700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>508800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>656300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>237900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>789300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>449500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>510800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>203300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>306700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>246700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>249300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>37700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>310300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>233500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3230,8 +3291,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3242,20 +3303,20 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
       </c>
       <c r="AI29" s="3">
-        <v>-68600</v>
+        <v>0</v>
       </c>
       <c r="AJ29" s="3">
         <v>-68600</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
+      <c r="AK29" s="3">
+        <v>-68600</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,53 +3583,56 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E32" s="3">
         <v>46400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>25900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>15400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>165100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>44200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-47300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-121000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-76800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-44800</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3638,130 +3708,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>304800</v>
+      </c>
+      <c r="E33" s="3">
         <v>229400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>490200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>591000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>477400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>519500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1096200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1162700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>954300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>719300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1361300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1109000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>871700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>596500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1308900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1451600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1801600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>498600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1178100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1390200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1808900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>989000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>872800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>658600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>511100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>394100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>667700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>508800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>656300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>237900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>789300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>449500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>442200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>134700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>306700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>246700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>249300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>37700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>310300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>233500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>304800</v>
+      </c>
+      <c r="E35" s="3">
         <v>229400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>490200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>591000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>477400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>519500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1096200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1162700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>954300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>719300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1361300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1109000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>871700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>596500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1308900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1451600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1801600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>498600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1178100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1390200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1808900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>989000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>872800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>658600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>511100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>394100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>667700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>508800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>656300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>237900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>789300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>449500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>442200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>134700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>306700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>246700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>249300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>37700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>310300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>233500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
         <v>46081</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45991</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45900</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45808</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45716</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45626</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45535</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45443</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45351</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45260</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45169</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45077</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44985</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44895</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44804</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44712</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44620</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44530</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44439</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44347</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44255</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44165</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44074</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43982</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43890</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43799</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43708</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43616</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43524</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43434</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43343</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43159</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43069</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42978</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42886</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42794</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42704</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,166 +4305,170 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1849100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2142500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3497400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1446100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1205000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2327900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4734300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4095800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3626200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4979900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6315000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3921900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4028000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4079900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4778700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1504000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1516700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1571800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2921700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2779100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2737600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2568800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2863000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2209100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1641900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1052500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1446000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1045500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>993500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1037900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1585300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1048400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1153900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1029600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2650900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>837700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>984000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>929100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1329500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>816100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>6832700</v>
+        <v>4400</v>
       </c>
       <c r="E42" s="3">
-        <v>6398700</v>
+        <v>7800</v>
       </c>
       <c r="F42" s="3">
-        <v>6027900</v>
+        <v>15100</v>
       </c>
       <c r="G42" s="3">
-        <v>5279600</v>
+        <v>15400</v>
       </c>
       <c r="H42" s="3">
-        <v>5172100</v>
+        <v>14000</v>
       </c>
       <c r="I42" s="3">
-        <v>3658000</v>
+        <v>10800</v>
       </c>
       <c r="J42" s="3">
+        <v>32600</v>
+      </c>
+      <c r="K42" s="3">
         <v>2980000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2754800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2408900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2002200</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -4463,275 +4553,284 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1011500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1000800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1041300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>994000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1029900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1107200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1106800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1060600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>984600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>980000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>980100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>948400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>735600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>670600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1500100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1272100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1000900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>815100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1198400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>777900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>776000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>795600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>851500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>612700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>894100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>593800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>406000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>550500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>534000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>576800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>968000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>557100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>502000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>560300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>450900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>373500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>296200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>223200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>516500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>453800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12584300</v>
+      </c>
+      <c r="E44" s="3">
         <v>12334900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11841300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>13700200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14516800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14251900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>20312400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>20640500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>20509700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19942800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>18897700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22579000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>22166600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>22067800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>21862500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>23272400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>22489900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>20988200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>19169400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>19457700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>18735800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>17982500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>17175100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>18007800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>18275900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>19000500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>17776500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>18848200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>18774500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>18208800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>17068700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>17569100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>17395000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>17580800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>10860900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>10921600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>10433200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>10468700</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>9178900</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>9655700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>7061900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6824900</v>
+      </c>
+      <c r="F45" s="3">
+        <v>6383600</v>
+      </c>
+      <c r="G45" s="3">
+        <v>6012500</v>
+      </c>
+      <c r="H45" s="3">
+        <v>5265600</v>
+      </c>
+      <c r="I45" s="3">
+        <v>5161300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3625400</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
@@ -4751,8 +4850,8 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25238100</v>
+      </c>
+      <c r="E46" s="3">
         <v>24715800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25754200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25117000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24685600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25434200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>32924900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>31444300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>30514500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>30941400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>31309200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29362700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>28784600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>28620700</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,141 +5053,147 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2576000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2576800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2805800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3864800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3841700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3779800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2616000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2585000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2514000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2415300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2355200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2503900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2508400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2533600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2867300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2969200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2954300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3058100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3321400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3564400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3019800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3136200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2510700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2426900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2422500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3509600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4441700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3628000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3763900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3326300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4161400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3324200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3478100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2992000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>3152500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>3045700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>3345300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2628400</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2831400</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>2422600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3">
         <v>642800</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
@@ -5093,11 +5201,11 @@
       <c r="H48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
         <v>516200</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
@@ -5105,11 +5213,11 @@
       <c r="L48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>404800</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>8</v>
@@ -5117,86 +5225,89 @@
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R48" s="3">
         <v>150000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>152000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>149800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>152100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>155600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>157200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>157400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>164600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>113400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>121700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>128400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>143700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>315100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>284600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>348000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>332600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>277900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>294100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>268100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>332300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>208600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>180000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>171100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>161300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>139700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>148200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5240,7 +5351,7 @@
         <v>3442400</v>
       </c>
       <c r="Q49" s="3">
-        <v>3632100</v>
+        <v>3442400</v>
       </c>
       <c r="R49" s="3">
         <v>3632100</v>
@@ -5273,7 +5384,7 @@
         <v>3632100</v>
       </c>
       <c r="AB49" s="3">
-        <v>3657900</v>
+        <v>3632100</v>
       </c>
       <c r="AC49" s="3">
         <v>3657900</v>
@@ -5288,37 +5399,40 @@
         <v>3657900</v>
       </c>
       <c r="AG49" s="3">
+        <v>3657900</v>
+      </c>
+      <c r="AH49" s="3">
         <v>3680000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3689200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3664900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3644100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>196400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>200100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>196500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>203100</v>
-      </c>
-      <c r="AO49" s="3">
-        <v>39800</v>
       </c>
       <c r="AP49" s="3">
         <v>39800</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>39800</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2019200</v>
+      </c>
+      <c r="E52" s="3">
         <v>2044700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1237600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2004600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1976000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1881500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1180000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1830200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1780500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1713000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1038300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1691900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1693000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1542900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1813400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1307400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1308800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1233400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1670300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1287400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1060800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1121000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1559800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1110100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1178300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>22600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>22700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>24400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>27500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>24700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>47400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>35100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>42500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>54600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>43200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>54100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>25700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>247600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>215800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>315700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33701500</v>
+      </c>
+      <c r="E54" s="3">
         <v>33210300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>34430400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>34878400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>34374500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>34986100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>41312800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39741000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38667700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>38951200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39234300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>37438100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36857700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36573200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>37984300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35339900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34306200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32635300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33207800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32744200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>31223200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>30552000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29935200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>29315300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>29309000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>29173700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>29359500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29459400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>29583100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>28749900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>28566200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>28289400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>28351100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>27944000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>18745000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>16939400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>16754500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>16230100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>15361800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>14998700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,175 +6145,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1953300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1921300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2026300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1735800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2355800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2167400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2127100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1788100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1727400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1565500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1631400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1721500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1490800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1616100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1552600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1555300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1321100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1321200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1230600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1171400</v>
-      </c>
-      <c r="X57" s="3">
-        <v>1037300</v>
       </c>
       <c r="Y57" s="3">
         <v>1037300</v>
       </c>
       <c r="Z57" s="3">
+        <v>1037300</v>
+      </c>
+      <c r="AA57" s="3">
         <v>1140300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1033600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1180700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1265200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1269600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1243600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1195600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1325400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1109200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>990800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>923900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>754700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>653000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>615900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>473800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>478500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>459200</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>442100</v>
+      </c>
+      <c r="E58" s="3">
         <v>465700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2207200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>25900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>48600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>577600</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>24100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>528300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>476700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>389900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>431900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>442100</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6194,55 +6328,55 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>1726000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1108400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>930100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>965000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1465800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>958300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1441700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1005300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1797100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1907300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1818900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1850200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1573200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>966600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>944600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>772200</v>
-      </c>
-      <c r="AK58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL58" s="3" t="s">
         <v>8</v>
@@ -6250,8 +6384,8 @@
       <c r="AM58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN58" s="3">
-        <v>0</v>
+      <c r="AN58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO58" s="3">
         <v>0</v>
@@ -6259,88 +6393,91 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>383200</v>
+      </c>
+      <c r="E59" s="3">
         <v>381700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>400600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>422900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>442100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>428900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>446200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>422300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>403400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>405600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>414800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>401300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>415200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>403300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>158800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>160600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>158600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>161200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>163500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>165100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>165800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>173700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>122800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>131300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>137800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>150800</v>
-      </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
@@ -6357,8 +6494,8 @@
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI59" s="3">
-        <v>0</v>
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ59" s="3">
         <v>0</v>
@@ -6381,53 +6518,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2966500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2967900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4854300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2390800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3022700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3403000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2783100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2234500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2659100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2447800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2049900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2512800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2548000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2336200</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,175 +6643,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3839200</v>
+      </c>
+      <c r="E61" s="3">
         <v>3849600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3808900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3773500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3009600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1889800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2258300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2471900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1875800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2466300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2816500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3079700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3584500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3760200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6199100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5562100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5984400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5853500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4652300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5542500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5894300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5976200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5955800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7180300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7495700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8115500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7776600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8375000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8840900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8531400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8543900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9647400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10355700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10821400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>7972500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>6860600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7342200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>6964600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>6275500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>6410300</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3166400</v>
+      </c>
+      <c r="E62" s="3">
         <v>3169500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3503500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4098700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4194200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5428900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6319200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5717100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5533700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5537900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5218900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4723600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4252200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4603600</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6747,8 +6893,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11935700</v>
+      </c>
+      <c r="E66" s="3">
         <v>11178100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12289800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12126800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11642700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12118800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13291600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12183300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11651900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12173300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12532300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11649600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11696600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12017900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13883800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12362600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12707900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11956200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12391400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12094000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11647100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11655700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11940300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>12143200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>12766300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13129100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13410000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14087500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14423800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13963100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13984600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14257400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>14759800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>14883100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>10872700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>9385100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>9431900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>9124100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>8335700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>8453200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22759100</v>
+      </c>
+      <c r="E72" s="3">
         <v>22577400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22471500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22107800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21646000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>21302100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25753100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>24791500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23764700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22949300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22369400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21113300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20111400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19350100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18861400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17647300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16288700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15078800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14685300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13570600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12241400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11488500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10565000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9760200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9132700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8654200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>8295000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>7633400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>7132900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6724200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6487700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5704700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5264700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4967600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4841000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4779000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4539200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4334900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4306300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4001900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21620600</v>
+      </c>
+      <c r="E76" s="3">
         <v>21879400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21959400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22570300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22579100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22728000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27870100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27412500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26877900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>26647800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>26580700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25656600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25015100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24418300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24100500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22977300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21598300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20679100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20816400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>20650200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19576100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>18896200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17994900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17172100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16542700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16044600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15949500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15371900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15159300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14786800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14581500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14032000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13591300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13060900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7872300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>7554300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>7322600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>7106100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>7026000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>6545500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
         <v>46081</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45991</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45900</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45808</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45716</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45626</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45535</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45443</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45351</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45260</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45169</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45077</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44985</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44895</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44804</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44712</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44620</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44530</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44439</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44347</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44255</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44165</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44074</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43982</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43890</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43799</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43708</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43616</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43524</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43434</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43343</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43251</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43159</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43069</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42978</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42886</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42794</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42704</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42613</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>304800</v>
+      </c>
+      <c r="E81" s="3">
         <v>229400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>490200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>591000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>477400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>519500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1096200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1162700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>954300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>719300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1361300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1109000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>871700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>596500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1308900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1451600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1801600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>498600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1178100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1390200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1808900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>989000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>872800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>658600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>511100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>394100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>667700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>508800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>656300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>237900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>789300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>449500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>442200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>134700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>306700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>246700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>249300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>37700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>310300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>233500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E83" s="3">
         <v>31300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>29400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>28600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>27100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>37100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>18400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>19400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>29200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>18400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>39500</v>
-      </c>
-      <c r="T83" s="3">
-        <v>20100</v>
       </c>
       <c r="U83" s="3">
         <v>20100</v>
       </c>
       <c r="V83" s="3">
+        <v>20100</v>
+      </c>
+      <c r="W83" s="3">
         <v>21100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>44700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>22300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>25800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>24300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>24100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>20400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>28400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>22800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>41000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>18400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>24500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>25300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>41400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>19600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>19400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>17500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>29400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>11700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>14400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-284400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-433500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1759500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-158600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1095000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-289000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>974500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>819200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>241800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>367900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2589200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>951900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>660500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>978200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2714200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>498800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>52600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-72200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1220400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>594200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>718100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>385500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1294000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1586000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>927800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>383000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1184100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>728200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-429900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-524400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>962900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>714300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>34400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-142700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>669200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>487500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-159800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>79300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>510900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>172300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-85200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-32200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-56000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-41400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-72900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-46200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-22300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-29700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-25200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-29900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-17100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-16900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-21800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-47800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-27400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-48900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-58900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-40800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-44700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-47000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-25800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-21600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-15600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E94" s="3">
         <v>93400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>45900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>161400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>21500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-125700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>98000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-126900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-147900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-62000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-34400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-44200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-36400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-66700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-64800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-20000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>26100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-81100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-50100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-93400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-93400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-187200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>13200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>59000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>52200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-91600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-78000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>424900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-67600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-951300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1028200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>87700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-84000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-873500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-766100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>30800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>33000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E96" s="3">
         <v>123500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>126600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>129100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>133600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>131600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>134700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>135900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>138900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>139400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>105200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>107100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>110400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>107900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-108300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-108700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-221000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-110100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-75800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-77700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-156300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-77800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-77900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-39000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-38900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-39200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-12900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-25900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-12900</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-13200</v>
       </c>
       <c r="AH96" s="3">
         <v>-13200</v>
       </c>
       <c r="AI96" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-22800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-9600</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-9400</v>
       </c>
       <c r="AL96" s="3">
         <v>-9400</v>
       </c>
       <c r="AM96" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-18800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-9400</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-9100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1095800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>268300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>443800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-175400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2134600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-169700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-527400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1455000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1529400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-80300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1109300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-574600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1483500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>547100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-434200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1390100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1257900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1102800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-484100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-817800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-629700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-580600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-917400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-158800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-789800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-844200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-731600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-53400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>69000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-877800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-752200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-565900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-450300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1056300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-549700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>687700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>286300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-28300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-204600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-221000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1435900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2073700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>278000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1109000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2402200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>679100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>389800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1340100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1309500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2446900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-191800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>41700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-541600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3264400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1402300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1350100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>143700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>29000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-149800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-337500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>700700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>575200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>581800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-393600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>398800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>48800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-574900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-533400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>510000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-105400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1497000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1621300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1813100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-146200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-345600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-400500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>513400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>600</v>
       </c>
     </row>
